--- a/output/catalog.xlsx
+++ b/output/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N302"/>
+  <dimension ref="A1:N301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18327,66 +18327,6 @@
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/344439646/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>344439646</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Платье вечернее нарядное</t>
-        </is>
-      </c>
-      <c r="D302" t="n">
-        <v>810</v>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Детское массажное масло идеально подходит для бережного очищения нежной кожи младенцев в первые месяцы жизни. Средство улучшает скольжение рук по коже, делая прикосновения еще более нежными и приятными. Воск из пророщенных зерен ячменя способствует уменьшению покраснений и шелушений, дарит ощущение максимального комфорта. Растительное масло кокоса быстро впитывается, насыщая кожу влагой и питательными веществами. Масла миндаля, виноградных косточек и жожоба прекрасно смягчают кожу и укрепляют ее гидролипидный барьер. Продукт на 100% состоит из натуральных ингредиентов, благодаря чему он идеален для детей с рождения. Эфирное масло органической лаванды дарит коже легкий цветочный аромат и оказывает ароматерапевтический эффект. Универсальное детское масло для массажа Botavikos не содержит силиконов, парабенов, минеральных масел, красителей, компонентов животного происхождения, не тестируется на животных! Безопасность компонентов средства клинически подтверждена, оно полностью гипоаллергенно, подходит как для малышей, так и для их мам, а также для беременных и кормящих женщин. Компания Botavikos является членом Международной федерации торговли эфирными маслами и ароматами (IFEAT) и Российской парфюмерно-косметической ассоциации (РПКА). Botavikos – растительный уход, который помогает восстановить естественные защитные силы и гармонизировать физиологические процессы. Попробуйте другие продукты, представленные в нашем ассортименте. Приятных Вам покупок!</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>https://images.wbstatic.net/big/new/344439646-1.jpg, https://images.wbstatic.net/big/new/344439646-2.jpg, https://images.wbstatic.net/big/new/344439646-3.jpg, https://images.wbstatic.net/big/new/344439646-4.jpg, https://images.wbstatic.net/big/new/344439646-5.jpg, https://images.wbstatic.net/big/new/344439646-6.jpg, https://images.wbstatic.net/big/new/344439646-7.jpg, https://images.wbstatic.net/big/new/344439646-8.jpg, https://images.wbstatic.net/big/new/344439646-9.jpg, https://images.wbstatic.net/big/new/344439646-10.jpg, https://images.wbstatic.net/big/new/344439646-11.jpg, https://images.wbstatic.net/big/new/344439646-12.jpg, https://images.wbstatic.net/big/new/344439646-13.jpg</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>CumAMORE</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/193502</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>38-40, 42-44, 46-48</t>
-        </is>
-      </c>
-      <c r="K302" t="n">
-        <v>0</v>
-      </c>
-      <c r="L302" t="n">
-        <v>5</v>
-      </c>
-      <c r="M302" t="n">
-        <v>5432</v>
-      </c>
-      <c r="N302" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
